--- a/resources/templates/standard/F2100-07.xlsx
+++ b/resources/templates/standard/F2100-07.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>결 재</t>
   </si>
@@ -747,7 +750,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -785,21 +790,21 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -906,11 +911,11 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -927,13 +932,13 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
       <c r="V4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
@@ -959,7 +964,7 @@
       <c r="AR4" s="7"/>
       <c r="AS4" s="7"/>
       <c r="AT4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -987,51 +992,51 @@
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="8"/>
       <c r="Z5" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC5" s="8"/>
       <c r="AD5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE5" s="8"/>
       <c r="AF5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG5" s="8"/>
       <c r="AH5" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK5" s="8"/>
       <c r="AL5" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM5" s="8"/>
       <c r="AN5" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO5" s="8"/>
       <c r="AP5" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ5" s="8"/>
       <c r="AR5" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS5" s="8"/>
       <c r="AT5" s="7"/>
@@ -1248,48 +1253,48 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="24"/>
       <c r="C10" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
       <c r="F10" s="25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I10" s="26"/>
       <c r="J10" s="25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" s="25"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O10" s="25"/>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
       <c r="R10" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S10" s="27"/>
       <c r="T10" s="27"/>
       <c r="U10" s="27"/>
       <c r="V10" s="25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W10" s="25"/>
       <c r="X10" s="25"/>
       <c r="Y10" s="25"/>
       <c r="Z10" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA10" s="28"/>
       <c r="AB10" s="28"/>
@@ -1368,36 +1373,36 @@
       <c r="A12" s="24"/>
       <c r="B12" s="24"/>
       <c r="C12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
       <c r="J12" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
@@ -1478,7 +1483,7 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -1530,7 +1535,7 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -1582,7 +1587,7 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="30"/>
       <c r="C16" s="30"/>
@@ -1634,7 +1639,7 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
